--- a/docs/architecture/chart-templates-v2.xlsx
+++ b/docs/architecture/chart-templates-v2.xlsx
@@ -19,10 +19,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Read me'!$A$4:$B$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Code ranges'!$A$4:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Limited company'!$A$4:$L$113</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sole trader'!$A$4:$L$107</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Partnership'!$A$4:$L$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Landlord'!$A$4:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Limited company'!$A$4:$L$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sole trader'!$A$4:$L$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Partnership'!$A$4:$L$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Landlord'!$A$4:$L$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Platform changes'!$A$4:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Legal references'!$A$4:$C$19</definedName>
   </definedNames>
@@ -576,7 +576,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Sage 50 layout of ranges (see 'Code ranges'). The platform keeps one VAT control account, 2200.</t>
+          <t>Sage 50 layout of ranges (see 'Code ranges'), including Sage's three VAT accounts 2200, 2201 and 2202.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Creditors 2100; VAT 2200; payroll 2210-2240; long-term 2300-2399</t>
+          <t>Creditors 2100; VAT 2200 (output), 2201 (input), 2202 (liability); payroll 2210-2240; long-term 2300-2399</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -848,7 +848,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>109 accounts. HMRC categories and boxes are UNVERIFIED.</t>
+          <t>111 accounts. HMRC categories and boxes are UNVERIFIED.</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>VAT control account</t>
+          <t>Sales tax control account</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>System account. One control account, not Sage's 2200/2201/2202: the VAT engine posts to one (M4b)</t>
+          <t>System account. Output VAT: the VAT settings' output account</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
@@ -2121,12 +2121,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>PAYE and National Insurance</t>
+          <t>Purchase tax control account</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2136,13 +2136,17 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_PAYE</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
+          <t>CURRENT_LIABILITY_VAT</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>VAT_CONTROL</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VAT_CONTROL</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -2152,19 +2156,23 @@
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>System account. Input VAT: the VAT settings' input account</t>
+        </is>
+      </c>
       <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Net wages</t>
+          <t>VAT liability</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2174,13 +2182,13 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_OTHER</t>
+          <t>CURRENT_LIABILITY_VAT</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VAT_CONTROL</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2190,19 +2198,23 @@
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>The return's net amount, moved here when the return is filed and cleared when it is paid</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Pension contributions payable</t>
+          <t>PAYE and National Insurance</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2212,7 +2224,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_OTHER</t>
+          <t>CURRENT_LIABILITY_PAYE</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -2235,12 +2247,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CIS deductions payable</t>
+          <t>Net wages</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2250,7 +2262,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_PAYE</t>
+          <t>CURRENT_LIABILITY_OTHER</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -2266,23 +2278,19 @@
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Tax deducted from subcontractors, paid to HMRC</t>
-        </is>
-      </c>
+      <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Directors' loan accounts</t>
+          <t>Pension contributions payable</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -2308,23 +2316,19 @@
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>Read by the director-loan register (DEC-062)</t>
-        </is>
-      </c>
+      <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Bank loans</t>
+          <t>CIS deductions payable</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2334,7 +2338,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>LONG_TERM_LIABILITY</t>
+          <t>CURRENT_LIABILITY_PAYE</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -2345,14 +2349,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>The part due within a year is reclassified at the year end</t>
+          <t>Tax deducted from subcontractors, paid to HMRC</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr"/>
@@ -2361,12 +2365,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Hire purchase</t>
+          <t>Directors' loan accounts</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -2376,7 +2380,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>LONG_TERM_LIABILITY</t>
+          <t>CURRENT_LIABILITY_OTHER</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -2387,24 +2391,28 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Read by the director-loan register (DEC-062)</t>
+        </is>
+      </c>
       <c r="K41" s="4" t="inlineStr"/>
       <c r="L41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Corporation tax</t>
+          <t>Bank loans</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2414,7 +2422,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_TAX</t>
+          <t>LONG_TERM_LIABILITY</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2425,24 +2433,28 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
+          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>The part due within a year is reclassified at the year end</t>
+        </is>
+      </c>
       <c r="K42" s="4" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Mortgages</t>
+          <t>Hire purchase</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -2475,22 +2487,22 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Ordinary shares</t>
+          <t>Corporation tax</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>EQUITY</t>
+          <t>LIABILITY</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>SHARE_CAPITAL</t>
+          <t>CURRENT_LIABILITY_TAX</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2501,7 +2513,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>BS.CAPITAL.SHARE_CAPITAL</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
@@ -2513,22 +2525,22 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Preference shares</t>
+          <t>Mortgages</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>EQUITY</t>
+          <t>LIABILITY</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>SHARE_CAPITAL</t>
+          <t>LONG_TERM_LIABILITY</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -2539,7 +2551,7 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>BS.CAPITAL.SHARE_CAPITAL</t>
+          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
@@ -2551,12 +2563,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Other reserves</t>
+          <t>Ordinary shares</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2566,7 +2578,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>RESERVES</t>
+          <t>SHARE_CAPITAL</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2577,7 +2589,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>BS.CAPITAL.RESERVES</t>
+          <t>BS.CAPITAL.SHARE_CAPITAL</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr"/>
@@ -2589,12 +2601,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Profit and loss account</t>
+          <t>Preference shares</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2604,14 +2616,10 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>RETAINED_EARNINGS</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>RETAINED_EARNINGS</t>
-        </is>
-      </c>
+          <t>SHARE_CAPITAL</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>NOT_APPLICABLE</t>
@@ -2619,28 +2627,24 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>BS.CAPITAL.RESERVES</t>
+          <t>BS.CAPITAL.SHARE_CAPITAL</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
       <c r="I47" s="4" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>System account; receives the year-end closing journal (DEC-060)</t>
-        </is>
-      </c>
+      <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Dividends</t>
+          <t>Other reserves</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2650,7 +2654,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>DIVIDENDS</t>
+          <t>RESERVES</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2673,71 +2677,79 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Sales - standard rate</t>
+          <t>Profit and loss account</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>INCOME</t>
+          <t>EQUITY</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>SALES</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr"/>
+          <t>RETAINED_EARNINGS</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>RETAINED_EARNINGS</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>PL.TURNOVER</t>
+          <t>BS.CAPITAL.RESERVES</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="4" t="inlineStr"/>
-      <c r="J49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>System account; receives the year-end closing journal (DEC-060)</t>
+        </is>
+      </c>
       <c r="K49" s="4" t="inlineStr"/>
       <c r="L49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Sales - reduced rate</t>
+          <t>Dividends</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>INCOME</t>
+          <t>EQUITY</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>SALES</t>
+          <t>DIVIDENDS</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>PL.TURNOVER</t>
+          <t>BS.CAPITAL.RESERVES</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -2749,12 +2761,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Sales - zero rate</t>
+          <t>Sales - standard rate</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2787,12 +2799,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Sales - exempt</t>
+          <t>Sales - reduced rate</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2808,7 +2820,7 @@
       <c r="E52" s="4" t="inlineStr"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2825,12 +2837,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Sales - outside the scope of VAT</t>
+          <t>Sales - zero rate</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2846,7 +2858,7 @@
       <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -2863,12 +2875,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Discounts allowed</t>
+          <t>Sales - exempt</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2884,7 +2896,7 @@
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2894,23 +2906,19 @@
       </c>
       <c r="H54" s="4" t="inlineStr"/>
       <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>Debit balance: reduces turnover</t>
-        </is>
-      </c>
+      <c r="J54" s="4" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr"/>
       <c r="L54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Miscellaneous income</t>
+          <t>Sales - outside the scope of VAT</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2920,7 +2928,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -2931,7 +2939,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_INCOME</t>
+          <t>PL.TURNOVER</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -2943,12 +2951,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Commissions received</t>
+          <t>Discounts allowed</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2958,7 +2966,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2969,24 +2977,28 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_INCOME</t>
+          <t>PL.TURNOVER</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr"/>
       <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Debit balance: reduces turnover</t>
+        </is>
+      </c>
       <c r="K56" s="4" t="inlineStr"/>
       <c r="L56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Insurance claims received</t>
+          <t>Miscellaneous income</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3019,12 +3031,12 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Rent received</t>
+          <t>Commissions received</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3040,7 +3052,7 @@
       <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3050,23 +3062,19 @@
       </c>
       <c r="H58" s="4" t="inlineStr"/>
       <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>For an individual this is property income: report it on SA105, not SA103</t>
-        </is>
-      </c>
+      <c r="J58" s="4" t="inlineStr"/>
       <c r="K58" s="4" t="inlineStr"/>
       <c r="L58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Grants received</t>
+          <t>Insurance claims received</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3099,12 +3107,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Bank interest received</t>
+          <t>Rent received</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3114,25 +3122,25 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_INCOME</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_RECEIVABLE</t>
+          <t>PL.OTHER_INCOME</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
       <c r="I60" s="4" t="inlineStr"/>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Savings income on the SA100 for an individual</t>
+          <t>For an individual this is property income: report it on SA105, not SA103</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr"/>
@@ -3141,33 +3149,33 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Materials and goods purchased</t>
+          <t>Grants received</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>EXPENSE</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>COST_OF_SALES</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>PL.COST_OF_SALES</t>
+          <t>PL.OTHER_INCOME</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -3179,50 +3187,54 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Goods imported</t>
+          <t>Bank interest received</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>EXPENSE</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>COST_OF_SALES</t>
+          <t>INTEREST_INCOME</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>PL.COST_OF_SALES</t>
+          <t>PL.INTEREST_RECEIVABLE</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
       <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Savings income on the SA100 for an individual</t>
+        </is>
+      </c>
       <c r="K62" s="4" t="inlineStr"/>
       <c r="L62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Discounts taken</t>
+          <t>Materials and goods purchased</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3248,23 +3260,19 @@
       </c>
       <c r="H63" s="4" t="inlineStr"/>
       <c r="I63" s="4" t="inlineStr"/>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>Credit balance: reduces cost of sales</t>
-        </is>
-      </c>
+      <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr"/>
       <c r="L63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Carriage inwards</t>
+          <t>Goods imported</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3297,12 +3305,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Stock movement</t>
+          <t>Discounts taken</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3318,7 +3326,7 @@
       <c r="E65" s="4" t="inlineStr"/>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -3330,7 +3338,7 @@
       <c r="I65" s="4" t="inlineStr"/>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Opening stock less closing stock</t>
+          <t>Credit balance: reduces cost of sales</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr"/>
@@ -3339,12 +3347,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Direct labour</t>
+          <t>Carriage inwards</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3360,7 +3368,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -3377,12 +3385,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
+          <t>Stock movement</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3398,7 +3406,7 @@
       <c r="E67" s="4" t="inlineStr"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -3410,7 +3418,7 @@
       <c r="I67" s="4" t="inlineStr"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Construction Industry Scheme payments</t>
+          <t>Opening stock less closing stock</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr"/>
@@ -3419,12 +3427,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Wages and salaries</t>
+          <t>Direct labour</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3434,7 +3442,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>COST_OF_SALES</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -3445,7 +3453,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.COST_OF_SALES</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -3457,12 +3465,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Directors' remuneration</t>
+          <t>Subcontractors</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3472,25 +3480,25 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>COST_OF_SALES</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.COST_OF_SALES</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
       <c r="I69" s="4" t="inlineStr"/>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>Disclosed in the accounts notes</t>
+          <t>Construction Industry Scheme payments</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr"/>
@@ -3499,12 +3507,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Employer's National Insurance</t>
+          <t>Wages and salaries</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -3537,12 +3545,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Employer's pension contributions</t>
+          <t>Directors' remuneration</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -3568,19 +3576,23 @@
       </c>
       <c r="H71" s="4" t="inlineStr"/>
       <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Disclosed in the accounts notes</t>
+        </is>
+      </c>
       <c r="K71" s="4" t="inlineStr"/>
       <c r="L71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Staff welfare and training</t>
+          <t>Employer's National Insurance</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3596,7 +3608,7 @@
       <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -3613,12 +3625,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Employer's pension contributions</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3634,7 +3646,7 @@
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -3651,12 +3663,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Business rates</t>
+          <t>Staff welfare and training</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3672,7 +3684,7 @@
       <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -3689,12 +3701,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Premises insurance</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3710,7 +3722,7 @@
       <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -3727,12 +3739,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Business rates</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3748,7 +3760,7 @@
       <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -3765,12 +3777,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Premises insurance</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3786,7 +3798,7 @@
       <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -3803,12 +3815,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Water rates</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -3824,7 +3836,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -3841,12 +3853,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Motor fuel</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -3872,23 +3884,19 @@
       </c>
       <c r="H79" s="4" t="inlineStr"/>
       <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>Private use is disallowable for a sole trader</t>
-        </is>
-      </c>
+      <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Motor repairs and servicing</t>
+          <t>Water rates</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -3904,7 +3912,7 @@
       <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -3921,12 +3929,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Motor insurance and road tax</t>
+          <t>Motor fuel</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3942,7 +3950,7 @@
       <c r="E81" s="4" t="inlineStr"/>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -3952,19 +3960,23 @@
       </c>
       <c r="H81" s="4" t="inlineStr"/>
       <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Private use is disallowable for a sole trader</t>
+        </is>
+      </c>
       <c r="K81" s="4" t="inlineStr"/>
       <c r="L81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Vehicle leasing</t>
+          <t>Motor repairs and servicing</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3990,23 +4002,19 @@
       </c>
       <c r="H82" s="4" t="inlineStr"/>
       <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>Car lease restrictions apply for tax and VAT</t>
-        </is>
-      </c>
+      <c r="J82" s="4" t="inlineStr"/>
       <c r="K82" s="4" t="inlineStr"/>
       <c r="L82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Motor insurance and road tax</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -4022,7 +4030,7 @@
       <c r="E83" s="4" t="inlineStr"/>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -4032,23 +4040,19 @@
       </c>
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>Wholly and exclusively (see Samadian)</t>
-        </is>
-      </c>
+      <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Hotels and subsistence</t>
+          <t>Vehicle leasing</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4074,19 +4078,23 @@
       </c>
       <c r="H84" s="4" t="inlineStr"/>
       <c r="I84" s="4" t="inlineStr"/>
-      <c r="J84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>Car lease restrictions apply for tax and VAT</t>
+        </is>
+      </c>
       <c r="K84" s="4" t="inlineStr"/>
       <c r="L84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Staff entertaining</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4114,7 +4122,7 @@
       <c r="I85" s="4" t="inlineStr"/>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>Allowable when for staff only</t>
+          <t>Wholly and exclusively (see Samadian)</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr"/>
@@ -4123,12 +4131,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Client entertaining</t>
+          <t>Hotels and subsistence</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4154,23 +4162,19 @@
       </c>
       <c r="H86" s="4" t="inlineStr"/>
       <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>Disallowed for tax; input VAT blocked</t>
-        </is>
-      </c>
+      <c r="J86" s="4" t="inlineStr"/>
       <c r="K86" s="4" t="inlineStr"/>
       <c r="L86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Postage and courier</t>
+          <t>Staff entertaining</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4186,7 +4190,7 @@
       <c r="E87" s="4" t="inlineStr"/>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -4196,19 +4200,23 @@
       </c>
       <c r="H87" s="4" t="inlineStr"/>
       <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>Allowable when for staff only</t>
+        </is>
+      </c>
       <c r="K87" s="4" t="inlineStr"/>
       <c r="L87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Stationery and printing</t>
+          <t>Client entertaining</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4234,19 +4242,23 @@
       </c>
       <c r="H88" s="4" t="inlineStr"/>
       <c r="I88" s="4" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>Disallowed for tax; input VAT blocked</t>
+        </is>
+      </c>
       <c r="K88" s="4" t="inlineStr"/>
       <c r="L88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Telephone and internet</t>
+          <t>Postage and courier</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4262,7 +4274,7 @@
       <c r="E89" s="4" t="inlineStr"/>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
@@ -4279,12 +4291,12 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Software and subscriptions</t>
+          <t>Stationery and printing</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4317,12 +4329,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Advertising and marketing</t>
+          <t>Telephone and internet</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -4355,12 +4367,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Website costs</t>
+          <t>Software and subscriptions</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4386,23 +4398,19 @@
       </c>
       <c r="H92" s="4" t="inlineStr"/>
       <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>Development may be capital</t>
-        </is>
-      </c>
+      <c r="J92" s="4" t="inlineStr"/>
       <c r="K92" s="4" t="inlineStr"/>
       <c r="L92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Advertising and marketing</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4428,23 +4436,19 @@
       </c>
       <c r="H93" s="4" t="inlineStr"/>
       <c r="I93" s="4" t="inlineStr"/>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>Fees on capital items are disallowable</t>
-        </is>
-      </c>
+      <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr"/>
       <c r="L93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Accountancy fees</t>
+          <t>Website costs</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -4470,19 +4474,23 @@
       </c>
       <c r="H94" s="4" t="inlineStr"/>
       <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>Development may be capital</t>
+        </is>
+      </c>
       <c r="K94" s="4" t="inlineStr"/>
       <c r="L94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Consultancy fees</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -4508,19 +4516,23 @@
       </c>
       <c r="H95" s="4" t="inlineStr"/>
       <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>Fees on capital items are disallowable</t>
+        </is>
+      </c>
       <c r="K95" s="4" t="inlineStr"/>
       <c r="L95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Equipment hire</t>
+          <t>Accountancy fees</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -4553,12 +4565,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Repairs and maintenance</t>
+          <t>Consultancy fees</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4584,23 +4596,19 @@
       </c>
       <c r="H97" s="4" t="inlineStr"/>
       <c r="I97" s="4" t="inlineStr"/>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>Improvements are capital (see Odeon v Jones)</t>
-        </is>
-      </c>
+      <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr"/>
       <c r="L97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Bank interest paid</t>
+          <t>Equipment hire</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -4610,18 +4618,18 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr"/>
@@ -4633,12 +4641,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Repairs and maintenance</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4654,7 +4662,7 @@
       <c r="E99" s="4" t="inlineStr"/>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -4664,19 +4672,23 @@
       </c>
       <c r="H99" s="4" t="inlineStr"/>
       <c r="I99" s="4" t="inlineStr"/>
-      <c r="J99" s="4" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>Improvements are capital (see Odeon v Jones)</t>
+        </is>
+      </c>
       <c r="K99" s="4" t="inlineStr"/>
       <c r="L99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Card and payment processing fees</t>
+          <t>Bank interest paid</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -4686,18 +4698,18 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr"/>
@@ -4709,12 +4721,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Loan interest</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -4724,18 +4736,18 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
@@ -4747,12 +4759,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Hire purchase interest</t>
+          <t>Card and payment processing fees</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -4762,18 +4774,18 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr"/>
@@ -4785,12 +4797,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Loan interest</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -4800,7 +4812,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>DEPRECIATION</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr"/>
@@ -4811,28 +4823,24 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>PL.DEPRECIATION</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
       <c r="I103" s="4" t="inlineStr"/>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>Added back for tax; capital allowances instead</t>
-        </is>
-      </c>
+      <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr"/>
       <c r="L103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Amortisation</t>
+          <t>Hire purchase interest</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -4842,7 +4850,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>DEPRECIATION</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr"/>
@@ -4853,7 +4861,7 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>PL.DEPRECIATION</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr"/>
@@ -4865,12 +4873,12 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Profit or loss on disposal of fixed assets</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -4880,7 +4888,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>OTHER_EXPENSE</t>
+          <t>DEPRECIATION</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
@@ -4891,14 +4899,14 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_EXPENSES</t>
+          <t>PL.DEPRECIATION</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
       <c r="I105" s="4" t="inlineStr"/>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>Disallowable; balancing allowances instead</t>
+          <t>Added back for tax; capital allowances instead</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr"/>
@@ -4907,12 +4915,12 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Bad debts written off</t>
+          <t>Amortisation</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -4922,7 +4930,7 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>DEPRECIATION</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
@@ -4933,28 +4941,24 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.DEPRECIATION</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr"/>
       <c r="I106" s="4" t="inlineStr"/>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>General provisions are disallowable</t>
-        </is>
-      </c>
+      <c r="J106" s="4" t="inlineStr"/>
       <c r="K106" s="4" t="inlineStr"/>
       <c r="L106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Profit or loss on disposal of fixed assets</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -4982,7 +4986,7 @@
       <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>Usually disallowable; charity gifts relieved elsewhere</t>
+          <t>Disallowable; balancing allowances instead</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr"/>
@@ -4991,12 +4995,12 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Trade subscriptions</t>
+          <t>Bad debts written off</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -5012,7 +5016,7 @@
       <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -5022,19 +5026,23 @@
       </c>
       <c r="H108" s="4" t="inlineStr"/>
       <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="4" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>General provisions are disallowable</t>
+        </is>
+      </c>
       <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>General insurance</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -5044,35 +5052,39 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>OTHER_EXPENSE</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr"/>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.OTHER_EXPENSES</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
       <c r="I109" s="4" t="inlineStr"/>
-      <c r="J109" s="4" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>Usually disallowable; charity gifts relieved elsewhere</t>
+        </is>
+      </c>
       <c r="K109" s="4" t="inlineStr"/>
       <c r="L109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Sundry expenses</t>
+          <t>Trade subscriptions</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -5082,18 +5094,18 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>OTHER_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr"/>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_EXPENSES</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr"/>
@@ -5105,12 +5117,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Corporation tax charge</t>
+          <t>General insurance</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -5120,18 +5132,18 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>TAX_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr"/>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>PL.TAXATION</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
@@ -5143,95 +5155,171 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Suspense</t>
+          <t>Sundry expenses</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>ASSET</t>
+          <t>EXPENSE</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_ASSET_OTHER</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>SUSPENSE</t>
-        </is>
-      </c>
+          <t>OTHER_EXPENSE</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr"/>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+          <t>PL.OTHER_EXPENSES</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr"/>
       <c r="I112" s="4" t="inlineStr"/>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>System account; a balance raises an alert (DEC-044)</t>
-        </is>
-      </c>
+      <c r="J112" s="4" t="inlineStr"/>
       <c r="K112" s="4" t="inlineStr"/>
       <c r="L112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Mispostings</t>
+          <t>Corporation tax charge</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>ASSET</t>
+          <t>EXPENSE</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_ASSET_OTHER</t>
+          <t>TAX_EXPENSE</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr"/>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+          <t>PL.TAXATION</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
       <c r="I113" s="4" t="inlineStr"/>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>Must be cleared before the year end</t>
-        </is>
-      </c>
+      <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr"/>
       <c r="L113" s="4" t="inlineStr"/>
     </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>9998</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Suspense</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT_ASSET_OTHER</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>SUSPENSE</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr"/>
+      <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>System account; a balance raises an alert (DEC-044)</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr"/>
+      <c r="L114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Mispostings</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT_ASSET_OTHER</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="4" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>Must be cleared before the year end</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr"/>
+      <c r="L115" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L113"/>
+  <autoFilter ref="A4:L115"/>
   <dataValidations count="1">
-    <dataValidation sqref="K5:K133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approve,Change,Remove"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5245,7 +5333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5272,7 +5360,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>103 accounts. HMRC categories and boxes are UNVERIFIED.</t>
+          <t>105 accounts. HMRC categories and boxes are UNVERIFIED.</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6592,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>VAT control account</t>
+          <t>Sales tax control account</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -6536,7 +6624,7 @@
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>System account. One control account, not Sage's 2200/2201/2202: the VAT engine posts to one (M4b)</t>
+          <t>System account. Output VAT: the VAT settings' output account</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
@@ -6545,12 +6633,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>PAYE and National Insurance</t>
+          <t>Purchase tax control account</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -6560,13 +6648,17 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_PAYE</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
+          <t>CURRENT_LIABILITY_VAT</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>VAT_CONTROL</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VAT_CONTROL</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -6576,19 +6668,23 @@
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>System account. Input VAT: the VAT settings' input account</t>
+        </is>
+      </c>
       <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Net wages</t>
+          <t>VAT liability</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -6598,13 +6694,13 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_OTHER</t>
+          <t>CURRENT_LIABILITY_VAT</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VAT_CONTROL</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -6614,19 +6710,23 @@
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>The return's net amount, moved here when the return is filed and cleared when it is paid</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Pension contributions payable</t>
+          <t>PAYE and National Insurance</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -6636,7 +6736,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_OTHER</t>
+          <t>CURRENT_LIABILITY_PAYE</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -6659,12 +6759,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CIS deductions payable</t>
+          <t>Net wages</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -6674,7 +6774,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_PAYE</t>
+          <t>CURRENT_LIABILITY_OTHER</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -6690,23 +6790,19 @@
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Tax deducted from subcontractors, paid to HMRC</t>
-        </is>
-      </c>
+      <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Bank loans</t>
+          <t>Pension contributions payable</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -6716,7 +6812,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>LONG_TERM_LIABILITY</t>
+          <t>CURRENT_LIABILITY_OTHER</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -6727,28 +6823,24 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>The part due within a year is reclassified at the year end</t>
-        </is>
-      </c>
+      <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Hire purchase</t>
+          <t>CIS deductions payable</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -6758,7 +6850,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>LONG_TERM_LIABILITY</t>
+          <t>CURRENT_LIABILITY_PAYE</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -6769,24 +6861,28 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Tax deducted from subcontractors, paid to HMRC</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Mortgages</t>
+          <t>Bank loans</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -6812,29 +6908,33 @@
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>The part due within a year is reclassified at the year end</t>
+        </is>
+      </c>
       <c r="K41" s="4" t="inlineStr"/>
       <c r="L41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Capital introduced</t>
+          <t>Hire purchase</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>OWNER_CAPITAL (NEW)</t>
+          <t>LIABILITY</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>LONG_TERM_LIABILITY</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -6843,9 +6943,9 @@
           <t>NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>BS.CAPITAL.PROPRIETOR (NEW)</t>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
@@ -6857,29 +6957,25 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Profit and loss account</t>
+          <t>Mortgages</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>EQUITY</t>
+          <t>LIABILITY</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>RETAINED_EARNINGS</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>RETAINED_EARNINGS</t>
-        </is>
-      </c>
+          <t>LONG_TERM_LIABILITY</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>NOT_APPLICABLE</t>
@@ -6887,28 +6983,24 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>BS.CAPITAL.RESERVES</t>
+          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>System account; receives the year-end closing journal (DEC-060)</t>
-        </is>
-      </c>
+      <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr"/>
       <c r="L43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Drawings</t>
+          <t>Capital introduced</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6918,7 +7010,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>DRAWINGS (NEW)</t>
+          <t>OWNER_CAPITAL (NEW)</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -6934,115 +7026,107 @@
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Owner's wages are drawings, not wages</t>
-        </is>
-      </c>
+      <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr"/>
       <c r="L44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Sales - standard rate</t>
+          <t>Profit and loss account</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>INCOME</t>
+          <t>EQUITY</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>SALES</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr"/>
+          <t>RETAINED_EARNINGS</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>RETAINED_EARNINGS</t>
+        </is>
+      </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>PL.TURNOVER</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>SE: turnover</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>SA103F box 15</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr"/>
+          <t>BS.CAPITAL.RESERVES</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>System account; receives the year-end closing journal (DEC-060)</t>
+        </is>
+      </c>
       <c r="K45" s="4" t="inlineStr"/>
       <c r="L45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Sales - reduced rate</t>
+          <t>Drawings</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>INCOME</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>SALES</t>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>DRAWINGS (NEW)</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>PL.TURNOVER</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>SE: turnover</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>SA103F box 15</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr"/>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>BS.CAPITAL.PROPRIETOR (NEW)</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Owner's wages are drawings, not wages</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Sales - zero rate</t>
+          <t>Sales - standard rate</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -7083,12 +7167,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Sales - exempt</t>
+          <t>Sales - reduced rate</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -7104,7 +7188,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -7129,12 +7213,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Sales - outside the scope of VAT</t>
+          <t>Sales - zero rate</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -7150,7 +7234,7 @@
       <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -7175,12 +7259,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Discounts allowed</t>
+          <t>Sales - exempt</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -7196,7 +7280,7 @@
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -7214,23 +7298,19 @@
           <t>SA103F box 15</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>Debit balance: reduces turnover</t>
-        </is>
-      </c>
+      <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="4" t="inlineStr"/>
       <c r="L50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Miscellaneous income</t>
+          <t>Sales - outside the scope of VAT</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -7240,7 +7320,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -7251,17 +7331,17 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_INCOME</t>
+          <t>PL.TURNOVER</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>SE: other</t>
+          <t>SE: turnover</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 16</t>
+          <t>SA103F box 15</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
@@ -7271,12 +7351,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Commissions received</t>
+          <t>Discounts allowed</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -7286,7 +7366,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -7297,32 +7377,36 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_INCOME</t>
+          <t>PL.TURNOVER</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>SE: other</t>
+          <t>SE: turnover</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 16</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr"/>
+          <t>SA103F box 15</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>Debit balance: reduces turnover</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="inlineStr"/>
       <c r="L52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Insurance claims received</t>
+          <t>Miscellaneous income</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -7363,12 +7447,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Rent received</t>
+          <t>Commissions received</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -7384,7 +7468,7 @@
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -7394,27 +7478,27 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>SE: not business income</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>For an individual this is property income: report it on SA105, not SA103</t>
-        </is>
-      </c>
+          <t>SE: other</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>SA103F box 16</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr"/>
       <c r="L54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Grants received</t>
+          <t>Insurance claims received</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -7455,12 +7539,12 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Bank interest received</t>
+          <t>Rent received</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -7470,18 +7554,18 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_INCOME</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_RECEIVABLE</t>
+          <t>PL.OTHER_INCOME</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -7492,7 +7576,7 @@
       <c r="I56" s="4" t="inlineStr"/>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Savings income on the SA100 for an individual</t>
+          <t>For an individual this is property income: report it on SA105, not SA103</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr"/>
@@ -7501,43 +7585,43 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Materials and goods purchased</t>
+          <t>Grants received</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>EXPENSE</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>COST_OF_SALES</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>PL.COST_OF_SALES</t>
+          <t>PL.OTHER_INCOME</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>SE: costOfGoods</t>
+          <t>SE: other</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 17</t>
+          <t>SA103F box 16</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr"/>
@@ -7547,58 +7631,58 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Goods imported</t>
+          <t>Bank interest received</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>EXPENSE</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>COST_OF_SALES</t>
+          <t>INTEREST_INCOME</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>PL.COST_OF_SALES</t>
+          <t>PL.INTEREST_RECEIVABLE</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>SE: costOfGoods</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>SA103F box 17</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr"/>
+          <t>SE: not business income</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Savings income on the SA100 for an individual</t>
+        </is>
+      </c>
       <c r="K58" s="4" t="inlineStr"/>
       <c r="L58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Discounts taken</t>
+          <t>Materials and goods purchased</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -7632,23 +7716,19 @@
           <t>SA103F box 17</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>Credit balance: reduces cost of sales</t>
-        </is>
-      </c>
+      <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Carriage inwards</t>
+          <t>Goods imported</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -7689,12 +7769,12 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Stock movement</t>
+          <t>Discounts taken</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -7710,7 +7790,7 @@
       <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -7730,7 +7810,7 @@
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Opening stock less closing stock</t>
+          <t>Credit balance: reduces cost of sales</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr"/>
@@ -7739,12 +7819,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Direct labour</t>
+          <t>Carriage inwards</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -7760,7 +7840,7 @@
       <c r="E62" s="4" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -7770,12 +7850,12 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>SE: wagesAndStaffCosts</t>
+          <t>SE: costOfGoods</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 19</t>
+          <t>SA103F box 17</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr"/>
@@ -7785,12 +7865,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
+          <t>Stock movement</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -7806,7 +7886,7 @@
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -7816,17 +7896,17 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>SE: paymentsToSubcontractors</t>
+          <t>SE: costOfGoods</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 18</t>
+          <t>SA103F box 17</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Construction Industry Scheme payments</t>
+          <t>Opening stock less closing stock</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr"/>
@@ -7835,12 +7915,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Wages and salaries</t>
+          <t>Direct labour</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -7850,7 +7930,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>COST_OF_SALES</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
@@ -7861,7 +7941,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.COST_OF_SALES</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -7881,12 +7961,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Employer's National Insurance</t>
+          <t>Subcontractors</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -7896,43 +7976,47 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>COST_OF_SALES</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.COST_OF_SALES</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>SE: wagesAndStaffCosts</t>
+          <t>SE: paymentsToSubcontractors</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 19</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr"/>
+          <t>SA103F box 18</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Construction Industry Scheme payments</t>
+        </is>
+      </c>
       <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Employer's pension contributions</t>
+          <t>Wages and salaries</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -7973,12 +8057,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Staff welfare and training</t>
+          <t>Employer's National Insurance</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -7994,7 +8078,7 @@
       <c r="E67" s="4" t="inlineStr"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -8019,12 +8103,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Employer's pension contributions</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -8040,7 +8124,7 @@
       <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -8050,12 +8134,12 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>SE: premisesRunningCosts</t>
+          <t>SE: wagesAndStaffCosts</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 21</t>
+          <t>SA103F box 19</t>
         </is>
       </c>
       <c r="J68" s="4" t="inlineStr"/>
@@ -8065,12 +8149,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Business rates</t>
+          <t>Staff welfare and training</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -8086,7 +8170,7 @@
       <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -8096,12 +8180,12 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>SE: premisesRunningCosts</t>
+          <t>SE: wagesAndStaffCosts</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 21</t>
+          <t>SA103F box 19</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr"/>
@@ -8111,12 +8195,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Premises insurance</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -8132,7 +8216,7 @@
       <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -8157,12 +8241,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Use of home as office</t>
+          <t>Business rates</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -8196,23 +8280,19 @@
           <t>SA103F box 21</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>Flat rate or an apportionment of household costs</t>
-        </is>
-      </c>
+      <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr"/>
       <c r="L71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Premises insurance</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -8228,7 +8308,7 @@
       <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -8253,12 +8333,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Use of home as office</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -8274,7 +8354,7 @@
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -8292,19 +8372,23 @@
           <t>SA103F box 21</t>
         </is>
       </c>
-      <c r="J73" s="4" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>Flat rate or an apportionment of household costs</t>
+        </is>
+      </c>
       <c r="K73" s="4" t="inlineStr"/>
       <c r="L73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Water rates</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -8320,7 +8404,7 @@
       <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -8345,12 +8429,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Motor fuel</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -8376,31 +8460,27 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>SE: carVanTravelExpenses</t>
+          <t>SE: premisesRunningCosts</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 20</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>Private use is disallowable for a sole trader</t>
-        </is>
-      </c>
+          <t>SA103F box 21</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Motor repairs and servicing</t>
+          <t>Water rates</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -8416,7 +8496,7 @@
       <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -8426,12 +8506,12 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>SE: carVanTravelExpenses</t>
+          <t>SE: premisesRunningCosts</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 20</t>
+          <t>SA103F box 21</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr"/>
@@ -8441,12 +8521,12 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Motor insurance and road tax</t>
+          <t>Motor fuel</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -8462,7 +8542,7 @@
       <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -8480,19 +8560,23 @@
           <t>SA103F box 20</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>Private use is disallowable for a sole trader</t>
+        </is>
+      </c>
       <c r="K77" s="4" t="inlineStr"/>
       <c r="L77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Vehicle leasing</t>
+          <t>Motor repairs and servicing</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -8526,23 +8610,19 @@
           <t>SA103F box 20</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>Car lease restrictions apply for tax and VAT</t>
-        </is>
-      </c>
+      <c r="J78" s="4" t="inlineStr"/>
       <c r="K78" s="4" t="inlineStr"/>
       <c r="L78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Motor insurance and road tax</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -8558,7 +8638,7 @@
       <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -8576,23 +8656,19 @@
           <t>SA103F box 20</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>Wholly and exclusively (see Samadian)</t>
-        </is>
-      </c>
+      <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Hotels and subsistence</t>
+          <t>Vehicle leasing</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -8626,19 +8702,23 @@
           <t>SA103F box 20</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Car lease restrictions apply for tax and VAT</t>
+        </is>
+      </c>
       <c r="K80" s="4" t="inlineStr"/>
       <c r="L80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Staff entertaining</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -8664,17 +8744,17 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>SE: wagesAndStaffCosts</t>
+          <t>SE: carVanTravelExpenses</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 19</t>
+          <t>SA103F box 20</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>Allowable when for staff only</t>
+          <t>Wholly and exclusively (see Samadian)</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr"/>
@@ -8683,12 +8763,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Client entertaining</t>
+          <t>Hotels and subsistence</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -8714,31 +8794,27 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>SE: businessEntertainmentCosts</t>
+          <t>SE: carVanTravelExpenses</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 24 (disallowable)</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>Disallowed for tax; input VAT blocked</t>
-        </is>
-      </c>
+          <t>SA103F box 20</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr"/>
       <c r="K82" s="4" t="inlineStr"/>
       <c r="L82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Postage and courier</t>
+          <t>Staff entertaining</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -8754,7 +8830,7 @@
       <c r="E83" s="4" t="inlineStr"/>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -8764,27 +8840,31 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>SE: adminCosts</t>
+          <t>SE: wagesAndStaffCosts</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 23</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr"/>
+          <t>SA103F box 19</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>Allowable when for staff only</t>
+        </is>
+      </c>
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Stationery and printing</t>
+          <t>Client entertaining</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -8810,27 +8890,31 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>SE: adminCosts</t>
+          <t>SE: businessEntertainmentCosts</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 23</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr"/>
+          <t>SA103F box 24 (disallowable)</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>Disallowed for tax; input VAT blocked</t>
+        </is>
+      </c>
       <c r="K84" s="4" t="inlineStr"/>
       <c r="L84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Telephone and internet</t>
+          <t>Postage and courier</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -8846,7 +8930,7 @@
       <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -8871,12 +8955,12 @@
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Software and subscriptions</t>
+          <t>Stationery and printing</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -8917,12 +9001,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Advertising and marketing</t>
+          <t>Telephone and internet</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -8948,12 +9032,12 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>SE: advertisingCosts</t>
+          <t>SE: adminCosts</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 24</t>
+          <t>SA103F box 23</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr"/>
@@ -8963,12 +9047,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Website costs</t>
+          <t>Software and subscriptions</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -8994,31 +9078,27 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>SE: advertisingCosts</t>
+          <t>SE: adminCosts</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 24</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>Development may be capital</t>
-        </is>
-      </c>
+          <t>SA103F box 23</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="inlineStr"/>
       <c r="L88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Advertising and marketing</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -9044,31 +9124,27 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>SE: professionalFees</t>
+          <t>SE: advertisingCosts</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 28</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>Fees on capital items are disallowable</t>
-        </is>
-      </c>
+          <t>SA103F box 24</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr"/>
       <c r="L89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Accountancy fees</t>
+          <t>Website costs</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -9094,27 +9170,31 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>SE: professionalFees</t>
+          <t>SE: advertisingCosts</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 28</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr"/>
+          <t>SA103F box 24</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>Development may be capital</t>
+        </is>
+      </c>
       <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Consultancy fees</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -9148,19 +9228,23 @@
           <t>SA103F box 28</t>
         </is>
       </c>
-      <c r="J91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>Fees on capital items are disallowable</t>
+        </is>
+      </c>
       <c r="K91" s="4" t="inlineStr"/>
       <c r="L91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Equipment hire</t>
+          <t>Accountancy fees</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -9186,12 +9270,12 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>SE: otherExpenses</t>
+          <t>SE: professionalFees</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 30</t>
+          <t>SA103F box 28</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr"/>
@@ -9201,12 +9285,12 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Repairs and maintenance</t>
+          <t>Consultancy fees</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -9232,31 +9316,27 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>SE: maintenanceCosts</t>
+          <t>SE: professionalFees</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 22</t>
-        </is>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>Improvements are capital (see Odeon v Jones)</t>
-        </is>
-      </c>
+          <t>SA103F box 28</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr"/>
       <c r="L93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Bank interest paid</t>
+          <t>Equipment hire</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -9266,28 +9346,28 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr"/>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>SE: interestOnBankOtherLoans</t>
+          <t>SE: otherExpenses</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 25</t>
+          <t>SA103F box 30</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr"/>
@@ -9297,12 +9377,12 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Repairs and maintenance</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -9318,7 +9398,7 @@
       <c r="E95" s="4" t="inlineStr"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -9328,27 +9408,31 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>SE: financeCharges</t>
+          <t>SE: maintenanceCosts</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 26</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr"/>
+          <t>SA103F box 22</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>Improvements are capital (see Odeon v Jones)</t>
+        </is>
+      </c>
       <c r="K95" s="4" t="inlineStr"/>
       <c r="L95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Card and payment processing fees</t>
+          <t>Bank interest paid</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -9358,28 +9442,28 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>SE: financeCharges</t>
+          <t>SE: interestOnBankOtherLoans</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 26</t>
+          <t>SA103F box 25</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr"/>
@@ -9389,12 +9473,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Loan interest</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -9404,28 +9488,28 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr"/>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>SE: interestOnBankOtherLoans</t>
+          <t>SE: financeCharges</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 25</t>
+          <t>SA103F box 26</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr"/>
@@ -9435,12 +9519,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Hire purchase interest</t>
+          <t>Card and payment processing fees</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -9450,28 +9534,28 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>SE: interestOnBankOtherLoans</t>
+          <t>SE: financeCharges</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 25</t>
+          <t>SA103F box 26</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr"/>
@@ -9481,12 +9565,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Loan interest</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -9496,7 +9580,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>DEPRECIATION</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr"/>
@@ -9507,36 +9591,32 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>PL.DEPRECIATION</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>SE: depreciation</t>
+          <t>SE: interestOnBankOtherLoans</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 29 (disallowable)</t>
-        </is>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>Added back for tax; capital allowances instead</t>
-        </is>
-      </c>
+          <t>SA103F box 25</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr"/>
       <c r="L99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Profit or loss on disposal of fixed assets</t>
+          <t>Hire purchase interest</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -9546,7 +9626,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>OTHER_EXPENSE</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
@@ -9557,36 +9637,32 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_EXPENSES</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>SE: depreciation</t>
+          <t>SE: interestOnBankOtherLoans</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 29 (disallowable)</t>
-        </is>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>Disallowable; balancing allowances instead</t>
-        </is>
-      </c>
+          <t>SA103F box 25</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Bad debts written off</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -9596,7 +9672,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>DEPRECIATION</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
@@ -9607,22 +9683,22 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.DEPRECIATION</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>SE: irrecoverableDebts</t>
+          <t>SE: depreciation</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 27</t>
+          <t>SA103F box 29 (disallowable)</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>General provisions are disallowable</t>
+          <t>Added back for tax; capital allowances instead</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
@@ -9631,12 +9707,12 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Profit or loss on disposal of fixed assets</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -9662,17 +9738,17 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>SE: otherExpenses</t>
+          <t>SE: depreciation</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 30</t>
+          <t>SA103F box 29 (disallowable)</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>Usually disallowable; charity gifts relieved elsewhere</t>
+          <t>Disallowable; balancing allowances instead</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr"/>
@@ -9681,12 +9757,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Trade subscriptions</t>
+          <t>Bad debts written off</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -9702,7 +9778,7 @@
       <c r="E103" s="4" t="inlineStr"/>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
@@ -9712,27 +9788,31 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>SE: otherExpenses</t>
+          <t>SE: irrecoverableDebts</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 30</t>
-        </is>
-      </c>
-      <c r="J103" s="4" t="inlineStr"/>
+          <t>SA103F box 27</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>General provisions are disallowable</t>
+        </is>
+      </c>
       <c r="K103" s="4" t="inlineStr"/>
       <c r="L103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>General insurance</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -9742,18 +9822,18 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>OTHER_EXPENSE</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.OTHER_EXPENSES</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -9766,19 +9846,23 @@
           <t>SA103F box 30</t>
         </is>
       </c>
-      <c r="J104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>Usually disallowable; charity gifts relieved elsewhere</t>
+        </is>
+      </c>
       <c r="K104" s="4" t="inlineStr"/>
       <c r="L104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Sundry expenses</t>
+          <t>Trade subscriptions</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -9788,18 +9872,18 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>OTHER_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_EXPENSES</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -9819,95 +9903,187 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Suspense</t>
+          <t>General insurance</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>ASSET</t>
+          <t>EXPENSE</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_ASSET_OTHER</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>SUSPENSE</t>
-        </is>
-      </c>
+          <t>OVERHEADS</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr"/>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>BS.CURRENT_ASSETS.DEBTORS</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr"/>
-      <c r="I106" s="4" t="inlineStr"/>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>System account; a balance raises an alert (DEC-044)</t>
-        </is>
-      </c>
+          <t>PL.ADMIN_EXPENSES</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>SE: otherExpenses</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>SA103F box 30</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr"/>
       <c r="K106" s="4" t="inlineStr"/>
       <c r="L106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Mispostings</t>
+          <t>Sundry expenses</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>ASSET</t>
+          <t>EXPENSE</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_ASSET_OTHER</t>
+          <t>OTHER_EXPENSE</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>BS.CURRENT_ASSETS.DEBTORS</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>Must be cleared before the year end</t>
-        </is>
-      </c>
+          <t>PL.OTHER_EXPENSES</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>SE: otherExpenses</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>SA103F box 30</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr"/>
       <c r="L107" s="4" t="inlineStr"/>
     </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>9998</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Suspense</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT_ASSET_OTHER</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>SUSPENSE</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr"/>
+      <c r="I108" s="4" t="inlineStr"/>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>System account; a balance raises an alert (DEC-044)</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr"/>
+      <c r="L108" s="4" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Mispostings</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT_ASSET_OTHER</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>Must be cleared before the year end</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L107"/>
+  <autoFilter ref="A4:L109"/>
   <dataValidations count="1">
-    <dataValidation sqref="K5:K127" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K129" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approve,Change,Remove"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9921,7 +10097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9948,7 +10124,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>104 accounts. HMRC categories and boxes are UNVERIFIED.</t>
+          <t>106 accounts. HMRC categories and boxes are UNVERIFIED.</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11356,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>VAT control account</t>
+          <t>Sales tax control account</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11212,7 +11388,7 @@
       <c r="I34" s="4" t="inlineStr"/>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>System account. One control account, not Sage's 2200/2201/2202: the VAT engine posts to one (M4b)</t>
+          <t>System account. Output VAT: the VAT settings' output account</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
@@ -11221,12 +11397,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>PAYE and National Insurance</t>
+          <t>Purchase tax control account</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -11236,13 +11412,17 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_PAYE</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
+          <t>CURRENT_LIABILITY_VAT</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>VAT_CONTROL</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VAT_CONTROL</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -11252,19 +11432,23 @@
       </c>
       <c r="H35" s="4" t="inlineStr"/>
       <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>System account. Input VAT: the VAT settings' input account</t>
+        </is>
+      </c>
       <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Net wages</t>
+          <t>VAT liability</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -11274,13 +11458,13 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_OTHER</t>
+          <t>CURRENT_LIABILITY_VAT</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VAT_CONTROL</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -11290,19 +11474,23 @@
       </c>
       <c r="H36" s="4" t="inlineStr"/>
       <c r="I36" s="4" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>The return's net amount, moved here when the return is filed and cleared when it is paid</t>
+        </is>
+      </c>
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Pension contributions payable</t>
+          <t>PAYE and National Insurance</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11312,7 +11500,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_OTHER</t>
+          <t>CURRENT_LIABILITY_PAYE</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -11335,12 +11523,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CIS deductions payable</t>
+          <t>Net wages</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11350,7 +11538,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_LIABILITY_PAYE</t>
+          <t>CURRENT_LIABILITY_OTHER</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -11366,23 +11554,19 @@
       </c>
       <c r="H38" s="4" t="inlineStr"/>
       <c r="I38" s="4" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Tax deducted from subcontractors, paid to HMRC</t>
-        </is>
-      </c>
+      <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Bank loans</t>
+          <t>Pension contributions payable</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11392,7 +11576,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>LONG_TERM_LIABILITY</t>
+          <t>CURRENT_LIABILITY_OTHER</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -11403,28 +11587,24 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
       <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>The part due within a year is reclassified at the year end</t>
-        </is>
-      </c>
+      <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Hire purchase</t>
+          <t>CIS deductions payable</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -11434,7 +11614,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>LONG_TERM_LIABILITY</t>
+          <t>CURRENT_LIABILITY_PAYE</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -11445,24 +11625,28 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
       <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Tax deducted from subcontractors, paid to HMRC</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Mortgages</t>
+          <t>Bank loans</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -11488,29 +11672,33 @@
       </c>
       <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>The part due within a year is reclassified at the year end</t>
+        </is>
+      </c>
       <c r="K41" s="4" t="inlineStr"/>
       <c r="L41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Partner 1 capital account</t>
+          <t>Hire purchase</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>PARTNER_CAPITAL (NEW)</t>
+          <t>LIABILITY</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>LONG_TERM_LIABILITY</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -11519,40 +11707,36 @@
           <t>NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>BS.CAPITAL.PARTNERS (NEW)</t>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
       <c r="I42" s="4" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>One per partner: 3000 to 3099</t>
-        </is>
-      </c>
+      <c r="J42" s="4" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Partner 1 current account</t>
+          <t>Mortgages</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>PARTNER_CURRENT (NEW)</t>
+          <t>LIABILITY</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>LONG_TERM_LIABILITY</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -11561,30 +11745,26 @@
           <t>NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>BS.CAPITAL.PARTNERS (NEW)</t>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>One per partner: 3100 to 3199; profit shares credited here</t>
-        </is>
-      </c>
+      <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr"/>
       <c r="L43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Profit and loss account</t>
+          <t>Partner 1 capital account</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -11592,31 +11772,27 @@
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>RETAINED_EARNINGS</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>RETAINED_EARNINGS</t>
-        </is>
-      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>PARTNER_CAPITAL (NEW)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
           <t>NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>BS.CAPITAL.RESERVES</t>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>BS.CAPITAL.PARTNERS (NEW)</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
       <c r="I44" s="4" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>System account; receives the year-end closing journal (DEC-060)</t>
+          <t>One per partner: 3000 to 3099</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr"/>
@@ -11625,12 +11801,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Partner 1 drawings</t>
+          <t>Partner 1 current account</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -11640,7 +11816,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>DRAWINGS (NEW)</t>
+          <t>PARTNER_CURRENT (NEW)</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -11658,7 +11834,7 @@
       <c r="I45" s="4" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>One per partner: 3260 to 3299</t>
+          <t>One per partner: 3100 to 3199; profit shares credited here</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr"/>
@@ -11667,104 +11843,100 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Sales - standard rate</t>
+          <t>Profit and loss account</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>INCOME</t>
+          <t>EQUITY</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>SALES</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr"/>
+          <t>RETAINED_EARNINGS</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>RETAINED_EARNINGS</t>
+        </is>
+      </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>PL.TURNOVER</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>SE: turnover</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>SA103F box 15</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr"/>
+          <t>BS.CAPITAL.RESERVES</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>System account; receives the year-end closing journal (DEC-060)</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Sales - reduced rate</t>
+          <t>Partner 1 drawings</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>INCOME</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>SALES</t>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>DRAWINGS (NEW)</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>PL.TURNOVER</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>SE: turnover</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>SA103F box 15</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr"/>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>BS.CAPITAL.PARTNERS (NEW)</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>One per partner: 3260 to 3299</t>
+        </is>
+      </c>
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Sales - zero rate</t>
+          <t>Sales - standard rate</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -11805,12 +11977,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Sales - exempt</t>
+          <t>Sales - reduced rate</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -11826,7 +11998,7 @@
       <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -11851,12 +12023,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Sales - outside the scope of VAT</t>
+          <t>Sales - zero rate</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -11872,7 +12044,7 @@
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -11897,12 +12069,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Discounts allowed</t>
+          <t>Sales - exempt</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -11918,7 +12090,7 @@
       <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -11936,23 +12108,19 @@
           <t>SA103F box 15</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>Debit balance: reduces turnover</t>
-        </is>
-      </c>
+      <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Miscellaneous income</t>
+          <t>Sales - outside the scope of VAT</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -11962,7 +12130,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -11973,17 +12141,17 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_INCOME</t>
+          <t>PL.TURNOVER</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>SE: other</t>
+          <t>SE: turnover</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 16</t>
+          <t>SA103F box 15</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr"/>
@@ -11993,12 +12161,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Commissions received</t>
+          <t>Discounts allowed</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -12008,7 +12176,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -12019,32 +12187,36 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_INCOME</t>
+          <t>PL.TURNOVER</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>SE: other</t>
+          <t>SE: turnover</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 16</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr"/>
+          <t>SA103F box 15</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Debit balance: reduces turnover</t>
+        </is>
+      </c>
       <c r="K53" s="4" t="inlineStr"/>
       <c r="L53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Insurance claims received</t>
+          <t>Miscellaneous income</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -12085,12 +12257,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Rent received</t>
+          <t>Commissions received</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -12106,7 +12278,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -12116,27 +12288,27 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>SE: not business income</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>For an individual this is property income: report it on SA105, not SA103</t>
-        </is>
-      </c>
+          <t>SE: other</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>SA103F box 16</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr"/>
       <c r="L55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Grants received</t>
+          <t>Insurance claims received</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -12177,12 +12349,12 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Bank interest received</t>
+          <t>Rent received</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -12192,18 +12364,18 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_INCOME</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_RECEIVABLE</t>
+          <t>PL.OTHER_INCOME</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -12214,7 +12386,7 @@
       <c r="I57" s="4" t="inlineStr"/>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>Savings income on the SA100 for an individual</t>
+          <t>For an individual this is property income: report it on SA105, not SA103</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr"/>
@@ -12223,43 +12395,43 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Materials and goods purchased</t>
+          <t>Grants received</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>EXPENSE</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>COST_OF_SALES</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>PL.COST_OF_SALES</t>
+          <t>PL.OTHER_INCOME</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>SE: costOfGoods</t>
+          <t>SE: other</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 17</t>
+          <t>SA103F box 16</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr"/>
@@ -12269,58 +12441,58 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Goods imported</t>
+          <t>Bank interest received</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>EXPENSE</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>COST_OF_SALES</t>
+          <t>INTEREST_INCOME</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>PL.COST_OF_SALES</t>
+          <t>PL.INTEREST_RECEIVABLE</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>SE: costOfGoods</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>SA103F box 17</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr"/>
+          <t>SE: not business income</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Savings income on the SA100 for an individual</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Discounts taken</t>
+          <t>Materials and goods purchased</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -12354,23 +12526,19 @@
           <t>SA103F box 17</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>Credit balance: reduces cost of sales</t>
-        </is>
-      </c>
+      <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr"/>
       <c r="L60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Carriage inwards</t>
+          <t>Goods imported</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -12411,12 +12579,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Stock movement</t>
+          <t>Discounts taken</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -12432,7 +12600,7 @@
       <c r="E62" s="4" t="inlineStr"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -12452,7 +12620,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Opening stock less closing stock</t>
+          <t>Credit balance: reduces cost of sales</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr"/>
@@ -12461,12 +12629,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Direct labour</t>
+          <t>Carriage inwards</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -12482,7 +12650,7 @@
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -12492,12 +12660,12 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>SE: wagesAndStaffCosts</t>
+          <t>SE: costOfGoods</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 19</t>
+          <t>SA103F box 17</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr"/>
@@ -12507,12 +12675,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
+          <t>Stock movement</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -12528,7 +12696,7 @@
       <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -12538,17 +12706,17 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>SE: paymentsToSubcontractors</t>
+          <t>SE: costOfGoods</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 18</t>
+          <t>SA103F box 17</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>Construction Industry Scheme payments</t>
+          <t>Opening stock less closing stock</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr"/>
@@ -12557,12 +12725,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Wages and salaries</t>
+          <t>Direct labour</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -12572,7 +12740,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>COST_OF_SALES</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr"/>
@@ -12583,7 +12751,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.COST_OF_SALES</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -12603,12 +12771,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Employer's National Insurance</t>
+          <t>Subcontractors</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -12618,43 +12786,47 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>COST_OF_SALES</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.COST_OF_SALES</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>SE: wagesAndStaffCosts</t>
+          <t>SE: paymentsToSubcontractors</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 19</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr"/>
+          <t>SA103F box 18</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Construction Industry Scheme payments</t>
+        </is>
+      </c>
       <c r="K66" s="4" t="inlineStr"/>
       <c r="L66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Employer's pension contributions</t>
+          <t>Wages and salaries</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -12695,12 +12867,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Staff welfare and training</t>
+          <t>Employer's National Insurance</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -12716,7 +12888,7 @@
       <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -12741,12 +12913,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Employer's pension contributions</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -12762,7 +12934,7 @@
       <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -12772,12 +12944,12 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>SE: premisesRunningCosts</t>
+          <t>SE: wagesAndStaffCosts</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 21</t>
+          <t>SA103F box 19</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr"/>
@@ -12787,12 +12959,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Business rates</t>
+          <t>Staff welfare and training</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -12808,7 +12980,7 @@
       <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -12818,12 +12990,12 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>SE: premisesRunningCosts</t>
+          <t>SE: wagesAndStaffCosts</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 21</t>
+          <t>SA103F box 19</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr"/>
@@ -12833,12 +13005,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Premises insurance</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -12854,7 +13026,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -12879,12 +13051,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Use of home as office</t>
+          <t>Business rates</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -12918,23 +13090,19 @@
           <t>SA103F box 21</t>
         </is>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>Flat rate or an apportionment of household costs</t>
-        </is>
-      </c>
+      <c r="J72" s="4" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr"/>
       <c r="L72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Premises insurance</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -12950,7 +13118,7 @@
       <c r="E73" s="4" t="inlineStr"/>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -12975,12 +13143,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Use of home as office</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -12996,7 +13164,7 @@
       <c r="E74" s="4" t="inlineStr"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -13014,19 +13182,23 @@
           <t>SA103F box 21</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Flat rate or an apportionment of household costs</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Water rates</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -13042,7 +13214,7 @@
       <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -13067,12 +13239,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Motor fuel</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -13098,31 +13270,27 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>SE: carVanTravelExpenses</t>
+          <t>SE: premisesRunningCosts</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 20</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>Private use is disallowable for a sole trader</t>
-        </is>
-      </c>
+          <t>SA103F box 21</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr"/>
       <c r="K76" s="4" t="inlineStr"/>
       <c r="L76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Motor repairs and servicing</t>
+          <t>Water rates</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -13138,7 +13306,7 @@
       <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -13148,12 +13316,12 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>SE: carVanTravelExpenses</t>
+          <t>SE: premisesRunningCosts</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 20</t>
+          <t>SA103F box 21</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr"/>
@@ -13163,12 +13331,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Motor insurance and road tax</t>
+          <t>Motor fuel</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -13184,7 +13352,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -13202,19 +13370,23 @@
           <t>SA103F box 20</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr"/>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>Private use is disallowable for a sole trader</t>
+        </is>
+      </c>
       <c r="K78" s="4" t="inlineStr"/>
       <c r="L78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Vehicle leasing</t>
+          <t>Motor repairs and servicing</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -13248,23 +13420,19 @@
           <t>SA103F box 20</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>Car lease restrictions apply for tax and VAT</t>
-        </is>
-      </c>
+      <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Motor insurance and road tax</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -13280,7 +13448,7 @@
       <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -13298,23 +13466,19 @@
           <t>SA103F box 20</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>Wholly and exclusively (see Samadian)</t>
-        </is>
-      </c>
+      <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="4" t="inlineStr"/>
       <c r="L80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Hotels and subsistence</t>
+          <t>Vehicle leasing</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -13348,19 +13512,23 @@
           <t>SA103F box 20</t>
         </is>
       </c>
-      <c r="J81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Car lease restrictions apply for tax and VAT</t>
+        </is>
+      </c>
       <c r="K81" s="4" t="inlineStr"/>
       <c r="L81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Staff entertaining</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -13386,17 +13554,17 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>SE: wagesAndStaffCosts</t>
+          <t>SE: carVanTravelExpenses</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 19</t>
+          <t>SA103F box 20</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>Allowable when for staff only</t>
+          <t>Wholly and exclusively (see Samadian)</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr"/>
@@ -13405,12 +13573,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Client entertaining</t>
+          <t>Hotels and subsistence</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -13436,31 +13604,27 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>SE: businessEntertainmentCosts</t>
+          <t>SE: carVanTravelExpenses</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 24 (disallowable)</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>Disallowed for tax; input VAT blocked</t>
-        </is>
-      </c>
+          <t>SA103F box 20</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Postage and courier</t>
+          <t>Staff entertaining</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -13476,7 +13640,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -13486,27 +13650,31 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>SE: adminCosts</t>
+          <t>SE: wagesAndStaffCosts</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 23</t>
-        </is>
-      </c>
-      <c r="J84" s="4" t="inlineStr"/>
+          <t>SA103F box 19</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>Allowable when for staff only</t>
+        </is>
+      </c>
       <c r="K84" s="4" t="inlineStr"/>
       <c r="L84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Stationery and printing</t>
+          <t>Client entertaining</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -13532,27 +13700,31 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>SE: adminCosts</t>
+          <t>SE: businessEntertainmentCosts</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 23</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="inlineStr"/>
+          <t>SA103F box 24 (disallowable)</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>Disallowed for tax; input VAT blocked</t>
+        </is>
+      </c>
       <c r="K85" s="4" t="inlineStr"/>
       <c r="L85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Telephone and internet</t>
+          <t>Postage and courier</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -13568,7 +13740,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -13593,12 +13765,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Software and subscriptions</t>
+          <t>Stationery and printing</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -13639,12 +13811,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Advertising and marketing</t>
+          <t>Telephone and internet</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -13670,12 +13842,12 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>SE: advertisingCosts</t>
+          <t>SE: adminCosts</t>
         </is>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 24</t>
+          <t>SA103F box 23</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr"/>
@@ -13685,12 +13857,12 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Website costs</t>
+          <t>Software and subscriptions</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -13716,31 +13888,27 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>SE: advertisingCosts</t>
+          <t>SE: adminCosts</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 24</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>Development may be capital</t>
-        </is>
-      </c>
+          <t>SA103F box 23</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr"/>
       <c r="L89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Advertising and marketing</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -13766,31 +13934,27 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>SE: professionalFees</t>
+          <t>SE: advertisingCosts</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 28</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>Fees on capital items are disallowable</t>
-        </is>
-      </c>
+          <t>SA103F box 24</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Accountancy fees</t>
+          <t>Website costs</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -13816,27 +13980,31 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>SE: professionalFees</t>
+          <t>SE: advertisingCosts</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 28</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr"/>
+          <t>SA103F box 24</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>Development may be capital</t>
+        </is>
+      </c>
       <c r="K91" s="4" t="inlineStr"/>
       <c r="L91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Consultancy fees</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -13870,19 +14038,23 @@
           <t>SA103F box 28</t>
         </is>
       </c>
-      <c r="J92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>Fees on capital items are disallowable</t>
+        </is>
+      </c>
       <c r="K92" s="4" t="inlineStr"/>
       <c r="L92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Equipment hire</t>
+          <t>Accountancy fees</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -13908,12 +14080,12 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>SE: otherExpenses</t>
+          <t>SE: professionalFees</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 30</t>
+          <t>SA103F box 28</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr"/>
@@ -13923,12 +14095,12 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Repairs and maintenance</t>
+          <t>Consultancy fees</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -13954,31 +14126,27 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>SE: maintenanceCosts</t>
+          <t>SE: professionalFees</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 22</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>Improvements are capital (see Odeon v Jones)</t>
-        </is>
-      </c>
+          <t>SA103F box 28</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr"/>
       <c r="K94" s="4" t="inlineStr"/>
       <c r="L94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Bank interest paid</t>
+          <t>Equipment hire</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -13988,28 +14156,28 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>SE: interestOnBankOtherLoans</t>
+          <t>SE: otherExpenses</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 25</t>
+          <t>SA103F box 30</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr"/>
@@ -14019,12 +14187,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Repairs and maintenance</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -14040,7 +14208,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -14050,27 +14218,31 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>SE: financeCharges</t>
+          <t>SE: maintenanceCosts</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 26</t>
-        </is>
-      </c>
-      <c r="J96" s="4" t="inlineStr"/>
+          <t>SA103F box 22</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>Improvements are capital (see Odeon v Jones)</t>
+        </is>
+      </c>
       <c r="K96" s="4" t="inlineStr"/>
       <c r="L96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Card and payment processing fees</t>
+          <t>Bank interest paid</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -14080,28 +14252,28 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr"/>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>SE: financeCharges</t>
+          <t>SE: interestOnBankOtherLoans</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 26</t>
+          <t>SA103F box 25</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr"/>
@@ -14111,12 +14283,12 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Loan interest</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -14126,28 +14298,28 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr"/>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>SE: interestOnBankOtherLoans</t>
+          <t>SE: financeCharges</t>
         </is>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 25</t>
+          <t>SA103F box 26</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr"/>
@@ -14157,12 +14329,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Hire purchase interest</t>
+          <t>Card and payment processing fees</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -14172,28 +14344,28 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr"/>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>SE: interestOnBankOtherLoans</t>
+          <t>SE: financeCharges</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 25</t>
+          <t>SA103F box 26</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr"/>
@@ -14203,12 +14375,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Loan interest</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -14218,7 +14390,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>DEPRECIATION</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
@@ -14229,36 +14401,32 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>PL.DEPRECIATION</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>SE: depreciation</t>
+          <t>SE: interestOnBankOtherLoans</t>
         </is>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 29 (disallowable)</t>
-        </is>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>Added back for tax; capital allowances instead</t>
-        </is>
-      </c>
+          <t>SA103F box 25</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Profit or loss on disposal of fixed assets</t>
+          <t>Hire purchase interest</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -14268,7 +14436,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>OTHER_EXPENSE</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
@@ -14279,36 +14447,32 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_EXPENSES</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>SE: depreciation</t>
+          <t>SE: interestOnBankOtherLoans</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 29 (disallowable)</t>
-        </is>
-      </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>Disallowable; balancing allowances instead</t>
-        </is>
-      </c>
+          <t>SA103F box 25</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr"/>
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Bad debts written off</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -14318,7 +14482,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>DEPRECIATION</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
@@ -14329,22 +14493,22 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.DEPRECIATION</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>SE: irrecoverableDebts</t>
+          <t>SE: depreciation</t>
         </is>
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 27</t>
+          <t>SA103F box 29 (disallowable)</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
         <is>
-          <t>General provisions are disallowable</t>
+          <t>Added back for tax; capital allowances instead</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr"/>
@@ -14353,12 +14517,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Profit or loss on disposal of fixed assets</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -14384,17 +14548,17 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>SE: otherExpenses</t>
+          <t>SE: depreciation</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 30</t>
+          <t>SA103F box 29 (disallowable)</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>Usually disallowable; charity gifts relieved elsewhere</t>
+          <t>Disallowable; balancing allowances instead</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr"/>
@@ -14403,12 +14567,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Trade subscriptions</t>
+          <t>Bad debts written off</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -14424,7 +14588,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -14434,27 +14598,31 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>SE: otherExpenses</t>
+          <t>SE: irrecoverableDebts</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>SA103F box 30</t>
-        </is>
-      </c>
-      <c r="J104" s="4" t="inlineStr"/>
+          <t>SA103F box 27</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>General provisions are disallowable</t>
+        </is>
+      </c>
       <c r="K104" s="4" t="inlineStr"/>
       <c r="L104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>General insurance</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -14464,18 +14632,18 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>OTHER_EXPENSE</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.OTHER_EXPENSES</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -14488,19 +14656,23 @@
           <t>SA103F box 30</t>
         </is>
       </c>
-      <c r="J105" s="4" t="inlineStr"/>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>Usually disallowable; charity gifts relieved elsewhere</t>
+        </is>
+      </c>
       <c r="K105" s="4" t="inlineStr"/>
       <c r="L105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Sundry expenses</t>
+          <t>Trade subscriptions</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -14510,18 +14682,18 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>OTHER_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_EXPENSES</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -14541,95 +14713,187 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Suspense</t>
+          <t>General insurance</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>ASSET</t>
+          <t>EXPENSE</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_ASSET_OTHER</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>SUSPENSE</t>
-        </is>
-      </c>
+          <t>OVERHEADS</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr"/>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>BS.CURRENT_ASSETS.DEBTORS</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr"/>
-      <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>System account; a balance raises an alert (DEC-044)</t>
-        </is>
-      </c>
+          <t>PL.ADMIN_EXPENSES</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>SE: otherExpenses</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>SA103F box 30</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr"/>
       <c r="K107" s="4" t="inlineStr"/>
       <c r="L107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Mispostings</t>
+          <t>Sundry expenses</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>ASSET</t>
+          <t>EXPENSE</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_ASSET_OTHER</t>
+          <t>OTHER_EXPENSE</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>BS.CURRENT_ASSETS.DEBTORS</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr"/>
-      <c r="I108" s="4" t="inlineStr"/>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>Must be cleared before the year end</t>
-        </is>
-      </c>
+          <t>PL.OTHER_EXPENSES</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>SE: otherExpenses</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>SA103F box 30</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr"/>
       <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="4" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>9998</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Suspense</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT_ASSET_OTHER</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>SUSPENSE</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="inlineStr"/>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>System account; a balance raises an alert (DEC-044)</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr"/>
+      <c r="L109" s="4" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Mispostings</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT_ASSET_OTHER</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr"/>
+      <c r="I110" s="4" t="inlineStr"/>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>Must be cleared before the year end</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr"/>
+      <c r="L110" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L108"/>
+  <autoFilter ref="A4:L110"/>
   <dataValidations count="1">
-    <dataValidation sqref="K5:K128" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approve,Change,Remove"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14643,7 +14907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14670,7 +14934,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>36 accounts. HMRC categories and boxes are UNVERIFIED.</t>
+          <t>38 accounts. HMRC categories and boxes are UNVERIFIED.</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15470,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>VAT control account</t>
+          <t>Sales tax control account</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -15238,7 +15502,7 @@
       <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>System account. One control account, not Sage's 2200/2201/2202: the VAT engine posts to one (M4b)</t>
+          <t>System account. Output VAT: the VAT settings' output account</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -15247,12 +15511,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bank loans</t>
+          <t>Purchase tax control account</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -15262,25 +15526,29 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>LONG_TERM_LIABILITY</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
+          <t>CURRENT_LIABILITY_VAT</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>VAT_CONTROL</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VAT_CONTROL</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>The part due within a year is reclassified at the year end</t>
+          <t>System account. Input VAT: the VAT settings' input account</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
@@ -15289,12 +15557,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Mortgages</t>
+          <t>VAT liability</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -15304,45 +15572,49 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>LONG_TERM_LIABILITY</t>
+          <t>CURRENT_LIABILITY_VAT</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VAT_CONTROL</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
+          <t>BS.CREDITORS_WITHIN_ONE_YEAR</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>The return's net amount, moved here when the return is filed and cleared when it is paid</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Capital introduced</t>
+          <t>Bank loans</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>OWNER_CAPITAL (NEW)</t>
+          <t>LIABILITY</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>LONG_TERM_LIABILITY</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
@@ -15351,43 +15623,43 @@
           <t>NOT_APPLICABLE</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>BS.CAPITAL.PROPRIETOR (NEW)</t>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
       <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>The part due within a year is reclassified at the year end</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Profit and loss account</t>
+          <t>Mortgages</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>EQUITY</t>
+          <t>LIABILITY</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>RETAINED_EARNINGS</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>RETAINED_EARNINGS</t>
-        </is>
-      </c>
+          <t>LONG_TERM_LIABILITY</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
           <t>NOT_APPLICABLE</t>
@@ -15395,28 +15667,24 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>BS.CAPITAL.RESERVES</t>
+          <t>BS.CREDITORS_AFTER_ONE_YEAR</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
       <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>System account; receives the year-end closing journal (DEC-060)</t>
-        </is>
-      </c>
+      <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Drawings</t>
+          <t>Capital introduced</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -15426,7 +15694,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>DRAWINGS (NEW)</t>
+          <t>OWNER_CAPITAL (NEW)</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -15442,59 +15710,51 @@
       </c>
       <c r="H21" s="4" t="inlineStr"/>
       <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Owner's wages are drawings, not wages</t>
-        </is>
-      </c>
+      <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Rents received</t>
+          <t>Profit and loss account</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>INCOME</t>
+          <t>EQUITY</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>SALES</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
+          <t>RETAINED_EARNINGS</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>RETAINED_EARNINGS</t>
+        </is>
+      </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>NOT_APPLICABLE</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>PL.TURNOVER</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>UP: periodAmount</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>SA105 box 20</t>
-        </is>
-      </c>
+          <t>BS.CAPITAL.RESERVES</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Exempt unless the landlord opted to tax a commercial property</t>
+          <t>System account; receives the year-end closing journal (DEC-060)</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -15503,58 +15763,54 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Lease premiums</t>
+          <t>Drawings</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>INCOME</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>SALES</t>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>DRAWINGS (NEW)</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>PL.TURNOVER</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>UP: premiumsOfLeaseGrant</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>SA105 box 22</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>BS.CAPITAL.PROPRIETOR (NEW)</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Owner's wages are drawings, not wages</t>
+        </is>
+      </c>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Reverse premiums and inducements</t>
+          <t>Rents received</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -15564,43 +15820,47 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_INCOME</t>
+          <t>PL.TURNOVER</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>UP: reversePremiums</t>
+          <t>UP: periodAmount</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 23</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr"/>
+          <t>SA105 box 20</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Exempt unless the landlord opted to tax a commercial property</t>
+        </is>
+      </c>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Other property income</t>
+          <t>Lease premiums</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -15610,7 +15870,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>OTHER_INCOME</t>
+          <t>SALES</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -15621,17 +15881,17 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_INCOME</t>
+          <t>PL.TURNOVER</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>UP: otherIncome</t>
+          <t>UP: premiumsOfLeaseGrant</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 20</t>
+          <t>SA105 box 22</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
@@ -15641,43 +15901,43 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Rent, rates, insurance and ground rents</t>
+          <t>Reverse premiums and inducements</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>EXPENSE</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.OTHER_INCOME</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>UP: premisesRunningCosts</t>
+          <t>UP: reversePremiums</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 24</t>
+          <t>SA105 box 23</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
@@ -15687,43 +15947,43 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Travel for the property business</t>
+          <t>Other property income</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>EXPENSE</t>
+          <t>INCOME</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>OTHER_INCOME</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.OTHER_INCOME</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>UP: travelCosts</t>
+          <t>UP: otherIncome</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 29</t>
+          <t>SA105 box 20</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
@@ -15733,12 +15993,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Legal and professional fees</t>
+          <t>Rent, rates, insurance and ground rents</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -15754,7 +16014,7 @@
       <c r="E28" s="4" t="inlineStr"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -15764,31 +16024,27 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>UP: professionalFees</t>
+          <t>UP: premisesRunningCosts</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 27</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>Fees on buying a property are capital</t>
-        </is>
-      </c>
+          <t>SA105 box 24</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Accountancy fees</t>
+          <t>Travel for the property business</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -15814,12 +16070,12 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>UP: professionalFees</t>
+          <t>UP: travelCosts</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 27</t>
+          <t>SA105 box 29</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr"/>
@@ -15829,12 +16085,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Letting agent and management fees</t>
+          <t>Legal and professional fees</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -15868,19 +16124,23 @@
           <t>SA105 box 27</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Fees on buying a property are capital</t>
+        </is>
+      </c>
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Property repairs and maintenance</t>
+          <t>Accountancy fees</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -15906,31 +16166,27 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>UP: repairsAndMaintenance</t>
+          <t>UP: professionalFees</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 25</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Improvements are capital (see Law Shipping)</t>
-        </is>
-      </c>
+          <t>SA105 box 27</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Replacement of domestic items</t>
+          <t>Letting agent and management fees</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -15956,27 +16212,27 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>UP: annual adjustment (check)</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Relief for replacing furnishings in a dwelling; claimed annually, not quarterly</t>
-        </is>
-      </c>
+          <t>UP: professionalFees</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>SA105 box 27</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Costs of services provided, including wages</t>
+          <t>Property repairs and maintenance</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -16002,27 +16258,31 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>UP: costOfServices</t>
+          <t>UP: repairsAndMaintenance</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 28</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr"/>
+          <t>SA105 box 25</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Improvements are capital (see Law Shipping)</t>
+        </is>
+      </c>
       <c r="K33" s="4" t="inlineStr"/>
       <c r="L33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Replacement of domestic items</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -16038,7 +16298,7 @@
       <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>EXEMPT</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -16048,27 +16308,27 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>UP: other</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>SA105 box 29</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr"/>
+          <t>UP: annual adjustment (check)</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Relief for replacing furnishings in a dwelling; claimed annually, not quarterly</t>
+        </is>
+      </c>
       <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Mortgage interest - residential property</t>
+          <t>Costs of services provided, including wages</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -16078,47 +16338,43 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>UP: residentialFinancialCost</t>
+          <t>UP: costOfServices</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 44</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>Not deducted: relief is a basic-rate tax reduction</t>
-        </is>
-      </c>
+          <t>SA105 box 28</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Finance costs - non-residential property</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -16128,28 +16384,28 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>INTEREST_EXPENSE</t>
+          <t>OVERHEADS</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>EXEMPT</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>PL.INTEREST_PAYABLE</t>
+          <t>PL.ADMIN_EXPENSES</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>UP: financialCosts</t>
+          <t>UP: other</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 26</t>
+          <t>SA105 box 29</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr"/>
@@ -16159,12 +16415,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Bad debts written off</t>
+          <t>Mortgage interest - residential property</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -16174,7 +16430,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>OVERHEADS</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -16185,22 +16441,22 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>PL.ADMIN_EXPENSES</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>UP: other</t>
+          <t>UP: residentialFinancialCost</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 29</t>
+          <t>SA105 box 44</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>Rent that will not be collected</t>
+          <t>Not deducted: relief is a basic-rate tax reduction</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr"/>
@@ -16209,12 +16465,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Other allowable property expenses</t>
+          <t>Finance costs - non-residential property</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -16224,28 +16480,28 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>OTHER_EXPENSE</t>
+          <t>INTEREST_EXPENSE</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>VATABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>PL.OTHER_EXPENSES</t>
+          <t>PL.INTEREST_PAYABLE</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>UP: other</t>
+          <t>UP: financialCosts</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>SA105 box 29</t>
+          <t>SA105 box 26</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr"/>
@@ -16255,44 +16511,48 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Suspense</t>
+          <t>Bad debts written off</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ASSET</t>
+          <t>EXPENSE</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_ASSET_OTHER</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>SUSPENSE</t>
-        </is>
-      </c>
+          <t>OVERHEADS</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>OUT_OF_SCOPE</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>BS.CURRENT_ASSETS.DEBTORS</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
+          <t>PL.ADMIN_EXPENSES</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>UP: other</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>SA105 box 29</t>
+        </is>
+      </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>System account; a balance raises an alert (DEC-044)</t>
+          <t>Rent that will not be collected</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr"/>
@@ -16301,49 +16561,141 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Mispostings</t>
+          <t>Other allowable property expenses</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>ASSET</t>
+          <t>EXPENSE</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>CURRENT_ASSET_OTHER</t>
+          <t>OTHER_EXPENSE</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
+          <t>VATABLE</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>BS.CURRENT_ASSETS.DEBTORS</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>Must be cleared before the year end</t>
-        </is>
-      </c>
+          <t>PL.OTHER_EXPENSES</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>UP: other</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>SA105 box 29</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr"/>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>9998</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Suspense</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT_ASSET_OTHER</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>SUSPENSE</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>System account; a balance raises an alert (DEC-044)</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr"/>
+      <c r="L41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Mispostings</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>ASSET</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>CURRENT_ASSET_OTHER</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>BS.CURRENT_ASSETS.DEBTORS</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Must be cleared before the year end</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L40"/>
+  <autoFilter ref="A4:L42"/>
   <dataValidations count="1">
-    <dataValidation sqref="K5:K60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K5:K62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Approve,Change,Remove"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16453,12 +16805,12 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>One VAT control account</t>
+          <t>VAT accounts</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2200 only. Sage charts split VAT into 2200, 2201 and 2202; the platform's VAT engine posts to one control account and reports the boxes from the VAT facts.</t>
+          <t>Sage's three: 2200 output VAT and 2201 input VAT (the VAT settings' output and input accounts, which the engine already keeps apart) and 2202 VAT liability. Corrects DEC-080, which said the engine posts to one account (DEC-087).</t>
         </is>
       </c>
     </row>
